--- a/assets/sample_data/종단면도 1~57.xlsx
+++ b/assets/sample_data/종단면도 1~57.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="현재_통합_문서"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="615" windowWidth="14775" windowHeight="10125"/>
+    <workbookView xWindow="270" yWindow="615" windowWidth="9240" windowHeight="6390"/>
   </bookViews>
   <sheets>
     <sheet name="측점데이터" sheetId="3" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1051" uniqueCount="587">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1052" uniqueCount="588">
   <si>
     <t>측점</t>
   </si>
@@ -1881,7 +1881,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>기초터파기</t>
+    <t>기초바닥레벨</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>터파기깊이</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2395,23 +2399,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U89"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:V89"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="9" width="11.5" style="3" customWidth="1"/>
     <col min="10" max="10" width="9.5" style="3" customWidth="1"/>
     <col min="11" max="13" width="9" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12" style="3" customWidth="1"/>
     <col min="15" max="16" width="9" style="3" customWidth="1"/>
     <col min="17" max="17" width="5.25" style="3" customWidth="1"/>
     <col min="18" max="18" width="6.375" style="3" customWidth="1"/>
     <col min="19" max="19" width="5.5" style="3" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="7.375" style="3" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="5.125" style="3" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="1"/>
+    <col min="22" max="22" width="8.5" style="3" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:22" s="4" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -2475,8 +2481,11 @@
       <c r="U1" s="12" t="s">
         <v>580</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V1" s="12" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -2528,8 +2537,9 @@
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
       <c r="U2" s="16"/>
-    </row>
-    <row r="3" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V2" s="2"/>
+    </row>
+    <row r="3" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
@@ -2572,8 +2582,8 @@
         <v>27.130000000000003</v>
       </c>
       <c r="N3" s="2">
-        <f t="shared" ref="N3:N27" si="1">G3-4.899</f>
-        <v>22.030999999999999</v>
+        <f t="shared" ref="N3:N66" si="1">G3-R3</f>
+        <v>23.75</v>
       </c>
       <c r="O3" s="9">
         <v>2.3149999999999999</v>
@@ -2594,8 +2604,11 @@
       <c r="U3" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V3" s="2">
+        <v>8.58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
@@ -2639,7 +2652,7 @@
       </c>
       <c r="N4" s="2">
         <f t="shared" si="1"/>
-        <v>21.901</v>
+        <v>23.62</v>
       </c>
       <c r="O4" s="10">
         <v>2.3149999999999999</v>
@@ -2660,8 +2673,11 @@
       <c r="U4" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V4" s="2">
+        <v>9.26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -2705,7 +2721,7 @@
       </c>
       <c r="N5" s="2">
         <f t="shared" si="1"/>
-        <v>21.861000000000001</v>
+        <v>23.580000000000002</v>
       </c>
       <c r="O5" s="10">
         <v>2.3149999999999999</v>
@@ -2726,8 +2742,11 @@
       <c r="U5" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V5" s="2">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>44</v>
       </c>
@@ -2771,7 +2790,7 @@
       </c>
       <c r="N6" s="2">
         <f t="shared" si="1"/>
-        <v>21.831</v>
+        <v>23.55</v>
       </c>
       <c r="O6" s="10">
         <v>2.3149999999999999</v>
@@ -2792,8 +2811,11 @@
       <c r="U6" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V6" s="2">
+        <v>9.42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>52</v>
       </c>
@@ -2837,7 +2859,7 @@
       </c>
       <c r="N7" s="2">
         <f t="shared" si="1"/>
-        <v>21.791</v>
+        <v>23.51</v>
       </c>
       <c r="O7" s="9">
         <v>2.3149999999999999</v>
@@ -2858,8 +2880,11 @@
       <c r="U7" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V7" s="2">
+        <v>9.3000000000000007</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>61</v>
       </c>
@@ -2903,7 +2928,7 @@
       </c>
       <c r="N8" s="2">
         <f t="shared" si="1"/>
-        <v>21.760999999999999</v>
+        <v>23.48</v>
       </c>
       <c r="O8" s="9">
         <v>3.4550000000000001</v>
@@ -2924,8 +2949,11 @@
       <c r="U8" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V8" s="2">
+        <v>9.1999999999999993</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>70</v>
       </c>
@@ -2969,7 +2997,7 @@
       </c>
       <c r="N9" s="2">
         <f t="shared" si="1"/>
-        <v>21.750999999999998</v>
+        <v>23.47</v>
       </c>
       <c r="O9" s="9">
         <v>3.7050000000000001</v>
@@ -2990,8 +3018,11 @@
       <c r="U9" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V9" s="2">
+        <v>9.0500000000000007</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>79</v>
       </c>
@@ -3035,7 +3066,7 @@
       </c>
       <c r="N10" s="2">
         <f t="shared" si="1"/>
-        <v>21.710999999999999</v>
+        <v>23.43</v>
       </c>
       <c r="O10" s="9">
         <v>3.6629999999999998</v>
@@ -3056,8 +3087,11 @@
       <c r="U10" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V10" s="2">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>87</v>
       </c>
@@ -3101,7 +3135,7 @@
       </c>
       <c r="N11" s="2">
         <f t="shared" si="1"/>
-        <v>21.670999999999999</v>
+        <v>23.39</v>
       </c>
       <c r="O11" s="9">
         <v>3.4830000000000001</v>
@@ -3122,8 +3156,11 @@
       <c r="U11" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V11" s="2">
+        <v>1.26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
@@ -3167,7 +3204,7 @@
       </c>
       <c r="N12" s="2">
         <f t="shared" si="1"/>
-        <v>21.651</v>
+        <v>23.37</v>
       </c>
       <c r="O12" s="9">
         <v>3.4830000000000001</v>
@@ -3188,8 +3225,11 @@
       <c r="U12" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V12" s="2">
+        <v>1.2250000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -3233,7 +3273,7 @@
       </c>
       <c r="N13" s="2">
         <f t="shared" si="1"/>
-        <v>21.631</v>
+        <v>23.35</v>
       </c>
       <c r="O13" s="9">
         <v>3.4830000000000001</v>
@@ -3254,8 +3294,11 @@
       <c r="U13" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V13" s="2">
+        <v>1.214</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>110</v>
       </c>
@@ -3299,7 +3342,7 @@
       </c>
       <c r="N14" s="2">
         <f t="shared" si="1"/>
-        <v>21.590999999999998</v>
+        <v>23.31</v>
       </c>
       <c r="O14" s="9">
         <v>3.4830000000000001</v>
@@ -3320,8 +3363,11 @@
       <c r="U14" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V14" s="2">
+        <v>1.198</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>61</v>
       </c>
@@ -3365,7 +3411,7 @@
       </c>
       <c r="N15" s="2">
         <f t="shared" si="1"/>
-        <v>21.561</v>
+        <v>23.28</v>
       </c>
       <c r="O15" s="9">
         <v>3.4830000000000001</v>
@@ -3386,8 +3432,11 @@
       <c r="U15" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V15" s="2">
+        <v>1.1850000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>123</v>
       </c>
@@ -3431,7 +3480,7 @@
       </c>
       <c r="N16" s="2">
         <f t="shared" si="1"/>
-        <v>21.541</v>
+        <v>23.26</v>
       </c>
       <c r="O16" s="9">
         <v>3.4830000000000001</v>
@@ -3452,8 +3501,11 @@
       <c r="U16" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V16" s="2">
+        <v>1.2010000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>128</v>
       </c>
@@ -3497,7 +3549,7 @@
       </c>
       <c r="N17" s="2">
         <f t="shared" si="1"/>
-        <v>21.420999999999999</v>
+        <v>23.14</v>
       </c>
       <c r="O17" s="9">
         <v>3.4830000000000001</v>
@@ -3518,8 +3570,11 @@
       <c r="U17" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V17" s="2">
+        <v>1.3089999999999999</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>135</v>
       </c>
@@ -3563,7 +3618,7 @@
       </c>
       <c r="N18" s="2">
         <f t="shared" si="1"/>
-        <v>21.291</v>
+        <v>23.01</v>
       </c>
       <c r="O18" s="9">
         <v>3.4830000000000001</v>
@@ -3584,8 +3639,11 @@
       <c r="U18" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V18" s="2">
+        <v>1.417</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>35</v>
       </c>
@@ -3629,7 +3687,7 @@
       </c>
       <c r="N19" s="2">
         <f t="shared" si="1"/>
-        <v>21.250999999999998</v>
+        <v>22.97</v>
       </c>
       <c r="O19" s="9">
         <v>3.4830000000000001</v>
@@ -3650,8 +3708,11 @@
       <c r="U19" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V19" s="2">
+        <v>1.4550000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>150</v>
       </c>
@@ -3695,7 +3756,7 @@
       </c>
       <c r="N20" s="2">
         <f t="shared" si="1"/>
-        <v>21.230999999999998</v>
+        <v>22.95</v>
       </c>
       <c r="O20" s="9">
         <v>3.4830000000000001</v>
@@ -3716,8 +3777,11 @@
       <c r="U20" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V20" s="2">
+        <v>1.3560000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>157</v>
       </c>
@@ -3761,7 +3825,7 @@
       </c>
       <c r="N21" s="2">
         <f t="shared" si="1"/>
-        <v>21.201000000000001</v>
+        <v>22.92</v>
       </c>
       <c r="O21" s="9">
         <v>3.4830000000000001</v>
@@ -3782,8 +3846,11 @@
       <c r="U21" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="22" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V21" s="2">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>61</v>
       </c>
@@ -3827,7 +3894,7 @@
       </c>
       <c r="N22" s="2">
         <f t="shared" si="1"/>
-        <v>21.170999999999999</v>
+        <v>22.89</v>
       </c>
       <c r="O22" s="9">
         <v>3.4830000000000001</v>
@@ -3848,8 +3915,11 @@
       <c r="U22" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V22" s="2">
+        <v>1.075</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>170</v>
       </c>
@@ -3893,7 +3963,7 @@
       </c>
       <c r="N23" s="2">
         <f t="shared" si="1"/>
-        <v>21.160999999999998</v>
+        <v>22.88</v>
       </c>
       <c r="O23" s="9">
         <v>3.4830000000000001</v>
@@ -3914,8 +3984,11 @@
       <c r="U23" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V23" s="2">
+        <v>1.0840000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>176</v>
       </c>
@@ -3959,7 +4032,7 @@
       </c>
       <c r="N24" s="2">
         <f t="shared" si="1"/>
-        <v>21.061</v>
+        <v>22.78</v>
       </c>
       <c r="O24" s="9">
         <v>3.4830000000000001</v>
@@ -3980,8 +4053,11 @@
       <c r="U24" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V24" s="2">
+        <v>1.1439999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>185</v>
       </c>
@@ -4025,7 +4101,7 @@
       </c>
       <c r="N25" s="2">
         <f t="shared" si="1"/>
-        <v>20.960999999999999</v>
+        <v>22.68</v>
       </c>
       <c r="O25" s="9">
         <v>3.4830000000000001</v>
@@ -4046,8 +4122,11 @@
       <c r="U25" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V25" s="2">
+        <v>1.204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>35</v>
       </c>
@@ -4091,7 +4170,7 @@
       </c>
       <c r="N26" s="2">
         <f t="shared" si="1"/>
-        <v>20.930999999999997</v>
+        <v>22.65</v>
       </c>
       <c r="O26" s="9">
         <v>3.4830000000000001</v>
@@ -4112,8 +4191,11 @@
       <c r="U26" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V26" s="2">
+        <v>1.2250000000000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>199</v>
       </c>
@@ -4157,7 +4239,7 @@
       </c>
       <c r="N27" s="2">
         <f t="shared" si="1"/>
-        <v>20.861000000000001</v>
+        <v>22.580000000000002</v>
       </c>
       <c r="O27" s="9">
         <v>2.4809999999999999</v>
@@ -4178,8 +4260,11 @@
       <c r="U27" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V27" s="2">
+        <v>1.5229999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>207</v>
       </c>
@@ -4221,7 +4306,10 @@
         <f t="shared" si="0"/>
         <v>27.51</v>
       </c>
-      <c r="N28" s="15"/>
+      <c r="N28" s="2">
+        <f t="shared" si="1"/>
+        <v>25.67</v>
+      </c>
       <c r="O28" s="18"/>
       <c r="P28" s="18"/>
       <c r="Q28" s="15" t="s">
@@ -4231,8 +4319,9 @@
       <c r="S28" s="16"/>
       <c r="T28" s="16"/>
       <c r="U28" s="16"/>
-    </row>
-    <row r="29" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V28" s="2"/>
+    </row>
+    <row r="29" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>212</v>
       </c>
@@ -4274,7 +4363,10 @@
         <f t="shared" si="0"/>
         <v>27.490000000000002</v>
       </c>
-      <c r="N29" s="15"/>
+      <c r="N29" s="2">
+        <f t="shared" si="1"/>
+        <v>25.65</v>
+      </c>
       <c r="O29" s="18"/>
       <c r="P29" s="18"/>
       <c r="Q29" s="15" t="s">
@@ -4284,8 +4376,9 @@
       <c r="S29" s="16"/>
       <c r="T29" s="16"/>
       <c r="U29" s="16"/>
-    </row>
-    <row r="30" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V29" s="2"/>
+    </row>
+    <row r="30" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>217</v>
       </c>
@@ -4327,7 +4420,10 @@
         <f t="shared" si="0"/>
         <v>27.360000000000003</v>
       </c>
-      <c r="N30" s="15"/>
+      <c r="N30" s="2">
+        <f t="shared" si="1"/>
+        <v>25.5</v>
+      </c>
       <c r="O30" s="18"/>
       <c r="P30" s="18"/>
       <c r="Q30" s="15" t="s">
@@ -4337,8 +4433,9 @@
       <c r="S30" s="16"/>
       <c r="T30" s="16"/>
       <c r="U30" s="16"/>
-    </row>
-    <row r="31" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V30" s="2"/>
+    </row>
+    <row r="31" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>61</v>
       </c>
@@ -4380,7 +4477,10 @@
         <f t="shared" si="0"/>
         <v>27.1</v>
       </c>
-      <c r="N31" s="15"/>
+      <c r="N31" s="2">
+        <f t="shared" si="1"/>
+        <v>25.37</v>
+      </c>
       <c r="O31" s="18"/>
       <c r="P31" s="18"/>
       <c r="Q31" s="15" t="s">
@@ -4390,8 +4490,9 @@
       <c r="S31" s="16"/>
       <c r="T31" s="16"/>
       <c r="U31" s="16"/>
-    </row>
-    <row r="32" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V31" s="2"/>
+    </row>
+    <row r="32" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>226</v>
       </c>
@@ -4433,7 +4534,10 @@
         <f t="shared" si="0"/>
         <v>26.5</v>
       </c>
-      <c r="N32" s="15"/>
+      <c r="N32" s="2">
+        <f t="shared" si="1"/>
+        <v>25.36</v>
+      </c>
       <c r="O32" s="18"/>
       <c r="P32" s="18"/>
       <c r="Q32" s="15" t="s">
@@ -4443,8 +4547,9 @@
       <c r="S32" s="16"/>
       <c r="T32" s="16"/>
       <c r="U32" s="16"/>
-    </row>
-    <row r="33" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V32" s="2"/>
+    </row>
+    <row r="33" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>230</v>
       </c>
@@ -4487,8 +4592,8 @@
         <v>25.87</v>
       </c>
       <c r="N33" s="2">
-        <f t="shared" ref="N33:N38" si="2">G33-4.899</f>
-        <v>20.410999999999998</v>
+        <f t="shared" si="1"/>
+        <v>22.13</v>
       </c>
       <c r="O33" s="9">
         <v>2.7730000000000001</v>
@@ -4511,8 +4616,11 @@
       <c r="U33" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V33" s="2">
+        <v>1.266</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>35</v>
       </c>
@@ -4555,8 +4663,8 @@
         <v>25.650000000000002</v>
       </c>
       <c r="N34" s="2">
-        <f t="shared" si="2"/>
-        <v>20.390999999999998</v>
+        <f t="shared" si="1"/>
+        <v>22.11</v>
       </c>
       <c r="O34" s="9">
         <v>3.0750000000000002</v>
@@ -4579,8 +4687,11 @@
       <c r="U34" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V34" s="2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>243</v>
       </c>
@@ -4623,8 +4734,8 @@
         <v>25.44</v>
       </c>
       <c r="N35" s="2">
-        <f t="shared" si="2"/>
-        <v>20.340999999999998</v>
+        <f t="shared" si="1"/>
+        <v>22.06</v>
       </c>
       <c r="O35" s="9">
         <v>3.3149999999999999</v>
@@ -4647,8 +4758,11 @@
       <c r="U35" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V35" s="2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>250</v>
       </c>
@@ -4691,8 +4805,8 @@
         <v>25.360000000000003</v>
       </c>
       <c r="N36" s="2">
-        <f t="shared" si="2"/>
-        <v>20.260999999999999</v>
+        <f t="shared" si="1"/>
+        <v>21.98</v>
       </c>
       <c r="O36" s="9">
         <v>3.3149999999999999</v>
@@ -4715,8 +4829,11 @@
       <c r="U36" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V36" s="2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>61</v>
       </c>
@@ -4759,8 +4876,8 @@
         <v>25.290000000000003</v>
       </c>
       <c r="N37" s="2">
-        <f t="shared" si="2"/>
-        <v>20.190999999999999</v>
+        <f t="shared" si="1"/>
+        <v>21.91</v>
       </c>
       <c r="O37" s="9">
         <v>3.3149999999999999</v>
@@ -4781,8 +4898,11 @@
       <c r="U37" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="38" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V37" s="2">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>265</v>
       </c>
@@ -4825,8 +4945,8 @@
         <v>25.28</v>
       </c>
       <c r="N38" s="2">
-        <f t="shared" si="2"/>
-        <v>20.180999999999997</v>
+        <f t="shared" si="1"/>
+        <v>21.9</v>
       </c>
       <c r="O38" s="19"/>
       <c r="P38" s="19"/>
@@ -4845,8 +4965,11 @@
       <c r="U38" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="39" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V38" s="2">
+        <v>1.1100000000000001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>273</v>
       </c>
@@ -4888,7 +5011,10 @@
         <f t="shared" si="0"/>
         <v>25.270000000000003</v>
       </c>
-      <c r="N39" s="15"/>
+      <c r="N39" s="2">
+        <f t="shared" si="1"/>
+        <v>25.07</v>
+      </c>
       <c r="O39" s="18"/>
       <c r="P39" s="18"/>
       <c r="Q39" s="15" t="s">
@@ -4898,8 +5024,9 @@
       <c r="S39" s="16"/>
       <c r="T39" s="16"/>
       <c r="U39" s="16"/>
-    </row>
-    <row r="40" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V39" s="2"/>
+    </row>
+    <row r="40" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>278</v>
       </c>
@@ -4941,7 +5068,10 @@
         <f t="shared" si="0"/>
         <v>25.270000000000003</v>
       </c>
-      <c r="N40" s="15"/>
+      <c r="N40" s="2">
+        <f t="shared" si="1"/>
+        <v>25.07</v>
+      </c>
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
       <c r="Q40" s="15" t="s">
@@ -4951,8 +5081,9 @@
       <c r="S40" s="16"/>
       <c r="T40" s="16"/>
       <c r="U40" s="16"/>
-    </row>
-    <row r="41" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V40" s="2"/>
+    </row>
+    <row r="41" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>282</v>
       </c>
@@ -4995,8 +5126,8 @@
         <v>25.220000000000002</v>
       </c>
       <c r="N41" s="2">
-        <f t="shared" ref="N41:N80" si="3">G41-4.899</f>
-        <v>20.120999999999999</v>
+        <f t="shared" si="1"/>
+        <v>21.84</v>
       </c>
       <c r="O41" s="19"/>
       <c r="P41" s="9">
@@ -5017,8 +5148,11 @@
       <c r="U41" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="42" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V41" s="2">
+        <v>0.85099999999999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>290</v>
       </c>
@@ -5061,8 +5195,8 @@
         <v>24.950000000000003</v>
       </c>
       <c r="N42" s="2">
-        <f t="shared" si="3"/>
-        <v>19.850999999999999</v>
+        <f t="shared" si="1"/>
+        <v>21.57</v>
       </c>
       <c r="O42" s="9">
         <v>4.1749999999999998</v>
@@ -5085,8 +5219,11 @@
       <c r="U42" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="43" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V42" s="2">
+        <v>0.96899999999999997</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>35</v>
       </c>
@@ -5129,8 +5266,8 @@
         <v>24.860000000000003</v>
       </c>
       <c r="N43" s="2">
-        <f t="shared" si="3"/>
-        <v>19.760999999999999</v>
+        <f t="shared" si="1"/>
+        <v>21.48</v>
       </c>
       <c r="O43" s="9">
         <v>4.3150000000000004</v>
@@ -5153,8 +5290,11 @@
       <c r="U43" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="44" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V43" s="2">
+        <v>1.01</v>
+      </c>
+    </row>
+    <row r="44" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>303</v>
       </c>
@@ -5197,8 +5337,8 @@
         <v>24.73</v>
       </c>
       <c r="N44" s="2">
-        <f t="shared" si="3"/>
-        <v>19.631</v>
+        <f t="shared" si="1"/>
+        <v>21.35</v>
       </c>
       <c r="O44" s="9">
         <v>5.3150000000000004</v>
@@ -5221,8 +5361,11 @@
       <c r="U44" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="45" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V44" s="2">
+        <v>0.97399999999999998</v>
+      </c>
+    </row>
+    <row r="45" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>309</v>
       </c>
@@ -5265,8 +5408,8 @@
         <v>24.53</v>
       </c>
       <c r="N45" s="2">
-        <f t="shared" si="3"/>
-        <v>19.430999999999997</v>
+        <f t="shared" si="1"/>
+        <v>21.15</v>
       </c>
       <c r="O45" s="9">
         <v>4.7149999999999999</v>
@@ -5289,8 +5432,11 @@
       <c r="U45" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="46" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V45" s="2">
+        <v>0.91800000000000004</v>
+      </c>
+    </row>
+    <row r="46" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>35</v>
       </c>
@@ -5333,8 +5479,8 @@
         <v>24.46</v>
       </c>
       <c r="N46" s="2">
-        <f t="shared" si="3"/>
-        <v>19.361000000000001</v>
+        <f t="shared" si="1"/>
+        <v>21.080000000000002</v>
       </c>
       <c r="O46" s="9">
         <v>3.5350000000000001</v>
@@ -5357,8 +5503,11 @@
       <c r="U46" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="47" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V46" s="2">
+        <v>0.89800000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>61</v>
       </c>
@@ -5401,8 +5550,8 @@
         <v>24.360000000000003</v>
       </c>
       <c r="N47" s="2">
-        <f t="shared" si="3"/>
-        <v>19.260999999999999</v>
+        <f t="shared" si="1"/>
+        <v>20.98</v>
       </c>
       <c r="O47" s="9">
         <v>1.3149999999999999</v>
@@ -5423,8 +5572,11 @@
       <c r="U47" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="48" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V47" s="2">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>329</v>
       </c>
@@ -5467,8 +5619,8 @@
         <v>24.35</v>
       </c>
       <c r="N48" s="2">
-        <f t="shared" si="3"/>
-        <v>19.250999999999998</v>
+        <f t="shared" si="1"/>
+        <v>20.414999999999999</v>
       </c>
       <c r="O48" s="9">
         <v>0.48299999999999998</v>
@@ -5489,8 +5641,11 @@
       <c r="U48" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="49" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V48" s="2">
+        <v>1.3979999999999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>336</v>
       </c>
@@ -5533,1505 +5688,1571 @@
         <v>24.34</v>
       </c>
       <c r="N49" s="2">
+        <f t="shared" si="1"/>
+        <v>20.405000000000001</v>
+      </c>
+      <c r="O49" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P49" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q49" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R49" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S49" s="2">
+        <v>6</v>
+      </c>
+      <c r="T49" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U49" s="2">
+        <v>34</v>
+      </c>
+      <c r="V49" s="2">
+        <v>1.3280000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="L50" s="6">
+        <f t="shared" si="0"/>
+        <v>24.310000000000002</v>
+      </c>
+      <c r="M50" s="6">
+        <f t="shared" si="0"/>
+        <v>24.310000000000002</v>
+      </c>
+      <c r="N50" s="2">
+        <f t="shared" si="1"/>
+        <v>20.375</v>
+      </c>
+      <c r="O50" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P50" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q50" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R50" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S50" s="2">
+        <v>6</v>
+      </c>
+      <c r="T50" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U50" s="2">
+        <v>34</v>
+      </c>
+      <c r="V50" s="2">
+        <v>1.222</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="J51" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="K51" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="L51" s="6">
+        <f t="shared" si="0"/>
+        <v>24.270000000000003</v>
+      </c>
+      <c r="M51" s="6">
+        <f t="shared" si="0"/>
+        <v>24.270000000000003</v>
+      </c>
+      <c r="N51" s="2">
+        <f t="shared" si="1"/>
+        <v>20.335000000000001</v>
+      </c>
+      <c r="O51" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P51" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q51" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R51" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S51" s="2">
+        <v>6</v>
+      </c>
+      <c r="T51" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U51" s="2">
+        <v>34</v>
+      </c>
+      <c r="V51" s="2">
+        <v>1.046</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="J52" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="K52" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="L52" s="6">
+        <f t="shared" si="0"/>
+        <v>24.25</v>
+      </c>
+      <c r="M52" s="6">
+        <f t="shared" si="0"/>
+        <v>24.25</v>
+      </c>
+      <c r="N52" s="2">
+        <f t="shared" si="1"/>
+        <v>20.315000000000001</v>
+      </c>
+      <c r="O52" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P52" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R52" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S52" s="2">
+        <v>6</v>
+      </c>
+      <c r="T52" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U52" s="2">
+        <v>34</v>
+      </c>
+      <c r="V52" s="2">
+        <v>0.98499999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="J53" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="K53" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="L53" s="6">
+        <f t="shared" si="0"/>
+        <v>24.220000000000002</v>
+      </c>
+      <c r="M53" s="6">
+        <f t="shared" si="0"/>
+        <v>24.220000000000002</v>
+      </c>
+      <c r="N53" s="2">
+        <f t="shared" si="1"/>
+        <v>20.285</v>
+      </c>
+      <c r="O53" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P53" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q53" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R53" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S53" s="2">
+        <v>6</v>
+      </c>
+      <c r="T53" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U53" s="2">
+        <v>34</v>
+      </c>
+      <c r="V53" s="2">
+        <v>0.97899999999999998</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="J54" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K54" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L54" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="M54" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="N54" s="2">
+        <f t="shared" si="1"/>
+        <v>20.234999999999999</v>
+      </c>
+      <c r="O54" s="9">
+        <v>-1.117</v>
+      </c>
+      <c r="P54" s="9">
+        <v>6.883</v>
+      </c>
+      <c r="Q54" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R54" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S54" s="2">
+        <v>6</v>
+      </c>
+      <c r="T54" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U54" s="2">
+        <v>34</v>
+      </c>
+      <c r="V54" s="2">
+        <v>0.96899999999999997</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="J55" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K55" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L55" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="M55" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="N55" s="2">
+        <f t="shared" si="1"/>
+        <v>20.215</v>
+      </c>
+      <c r="O55" s="9">
+        <v>-1.1519999999999999</v>
+      </c>
+      <c r="P55" s="9">
+        <v>6.8479999999999999</v>
+      </c>
+      <c r="Q55" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R55" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S55" s="2">
+        <v>6</v>
+      </c>
+      <c r="T55" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U55" s="2">
+        <v>34</v>
+      </c>
+      <c r="V55" s="2">
+        <v>0.96499999999999997</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="J56" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K56" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L56" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="M56" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="N56" s="2">
+        <f t="shared" si="1"/>
+        <v>20.215</v>
+      </c>
+      <c r="O56" s="9">
+        <v>-1.1519999999999999</v>
+      </c>
+      <c r="P56" s="9">
+        <v>6.8479999999999999</v>
+      </c>
+      <c r="Q56" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R56" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S56" s="2">
+        <v>6</v>
+      </c>
+      <c r="T56" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U56" s="2">
+        <v>34</v>
+      </c>
+      <c r="V56" s="2">
+        <v>0.96499999999999997</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L57" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="M57" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="N57" s="2">
+        <f t="shared" si="1"/>
+        <v>20.215</v>
+      </c>
+      <c r="O57" s="9">
+        <v>-1.1519999999999999</v>
+      </c>
+      <c r="P57" s="9">
+        <v>6.8479999999999999</v>
+      </c>
+      <c r="Q57" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R57" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S57" s="2">
+        <v>6</v>
+      </c>
+      <c r="T57" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U57" s="2">
+        <v>34</v>
+      </c>
+      <c r="V57" s="2">
+        <v>0.96499999999999997</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="K58" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="L58" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="M58" s="6">
+        <f t="shared" si="0"/>
+        <v>25.240000000000002</v>
+      </c>
+      <c r="N58" s="2">
+        <f t="shared" si="1"/>
+        <v>20.205000000000002</v>
+      </c>
+      <c r="O58" s="9">
+        <v>-0.67100000000000004</v>
+      </c>
+      <c r="P58" s="9">
+        <v>6.8289999999999997</v>
+      </c>
+      <c r="Q58" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R58" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S58" s="2">
+        <v>6</v>
+      </c>
+      <c r="T58" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U58" s="2">
+        <v>34</v>
+      </c>
+      <c r="V58" s="2">
+        <v>0.97099999999999997</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J59" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="K59" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="L59" s="6">
+        <f t="shared" si="0"/>
+        <v>24.05</v>
+      </c>
+      <c r="M59" s="6">
+        <f t="shared" si="0"/>
+        <v>24.05</v>
+      </c>
+      <c r="N59" s="2">
+        <f t="shared" si="1"/>
+        <v>20.115000000000002</v>
+      </c>
+      <c r="O59" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P59" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q59" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R59" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S59" s="2">
+        <v>6</v>
+      </c>
+      <c r="T59" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U59" s="2">
+        <v>34</v>
+      </c>
+      <c r="V59" s="2">
+        <v>1.0109999999999999</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="J60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L60" s="6">
+        <f t="shared" si="0"/>
+        <v>23.970000000000002</v>
+      </c>
+      <c r="M60" s="6">
+        <f t="shared" si="0"/>
+        <v>23.970000000000002</v>
+      </c>
+      <c r="N60" s="2">
+        <f t="shared" si="1"/>
+        <v>20.035</v>
+      </c>
+      <c r="O60" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P60" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q60" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R60" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S60" s="2">
+        <v>6</v>
+      </c>
+      <c r="T60" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U60" s="2">
+        <v>34</v>
+      </c>
+      <c r="V60" s="2">
+        <v>1.0509999999999999</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="L61" s="6">
+        <f t="shared" si="0"/>
+        <v>23.94</v>
+      </c>
+      <c r="M61" s="6">
+        <f t="shared" si="0"/>
+        <v>23.94</v>
+      </c>
+      <c r="N61" s="2">
+        <f t="shared" si="1"/>
+        <v>20.004999999999999</v>
+      </c>
+      <c r="O61" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P61" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q61" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R61" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S61" s="2">
+        <v>6</v>
+      </c>
+      <c r="T61" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U61" s="2">
+        <v>34</v>
+      </c>
+      <c r="V61" s="2">
+        <v>1.0649999999999999</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="J62" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="K62" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="L62" s="6">
+        <f t="shared" si="0"/>
+        <v>23.92</v>
+      </c>
+      <c r="M62" s="6">
+        <f t="shared" si="0"/>
+        <v>23.92</v>
+      </c>
+      <c r="N62" s="2">
+        <f t="shared" si="1"/>
+        <v>19.984999999999999</v>
+      </c>
+      <c r="O62" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P62" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q62" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R62" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S62" s="2">
+        <v>6</v>
+      </c>
+      <c r="T62" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U62" s="2">
+        <v>34</v>
+      </c>
+      <c r="V62" s="2">
+        <v>1.0569999999999999</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="L63" s="6">
+        <f t="shared" si="0"/>
+        <v>23.89</v>
+      </c>
+      <c r="M63" s="6">
+        <f t="shared" si="0"/>
+        <v>23.89</v>
+      </c>
+      <c r="N63" s="2">
+        <f t="shared" si="1"/>
+        <v>19.955000000000002</v>
+      </c>
+      <c r="O63" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P63" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q63" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R63" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S63" s="2">
+        <v>6</v>
+      </c>
+      <c r="T63" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U63" s="2">
+        <v>34</v>
+      </c>
+      <c r="V63" s="2">
+        <v>1.0449999999999999</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L64" s="6">
+        <f t="shared" si="0"/>
+        <v>23.860000000000003</v>
+      </c>
+      <c r="M64" s="6">
+        <f t="shared" si="0"/>
+        <v>23.860000000000003</v>
+      </c>
+      <c r="N64" s="2">
+        <f t="shared" si="1"/>
+        <v>19.925000000000001</v>
+      </c>
+      <c r="O64" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="P64" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q64" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R64" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S64" s="2">
+        <v>6</v>
+      </c>
+      <c r="T64" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U64" s="2">
+        <v>34</v>
+      </c>
+      <c r="V64" s="2">
+        <v>1.0349999999999999</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="L65" s="6">
+        <f t="shared" si="0"/>
+        <v>23.860000000000003</v>
+      </c>
+      <c r="M65" s="6">
+        <f t="shared" si="0"/>
+        <v>23.860000000000003</v>
+      </c>
+      <c r="N65" s="2">
+        <f t="shared" si="1"/>
+        <v>19.925000000000001</v>
+      </c>
+      <c r="O65" s="9">
+        <v>0.48299999999999998</v>
+      </c>
+      <c r="P65" s="9">
+        <v>8.4830000000000005</v>
+      </c>
+      <c r="Q65" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R65" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S65" s="2">
+        <v>6</v>
+      </c>
+      <c r="T65" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U65" s="2">
+        <v>34</v>
+      </c>
+      <c r="V65" s="2">
+        <v>1.0329999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J66" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="K66" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="L66" s="6">
+        <f t="shared" si="0"/>
+        <v>23.82</v>
+      </c>
+      <c r="M66" s="6">
+        <f t="shared" si="0"/>
+        <v>23.82</v>
+      </c>
+      <c r="N66" s="2">
+        <f t="shared" si="1"/>
+        <v>19.885000000000002</v>
+      </c>
+      <c r="O66" s="9">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="P66" s="9">
+        <v>8.7629999999999999</v>
+      </c>
+      <c r="Q66" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R66" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S66" s="2">
+        <v>6</v>
+      </c>
+      <c r="T66" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U66" s="2">
+        <v>34</v>
+      </c>
+      <c r="V66" s="2">
+        <v>1.0209999999999999</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="L67" s="6">
+        <f t="shared" ref="L67:M81" si="2">J67-0.4</f>
+        <v>23.790000000000003</v>
+      </c>
+      <c r="M67" s="6">
+        <f t="shared" si="2"/>
+        <v>23.790000000000003</v>
+      </c>
+      <c r="N67" s="2">
+        <f t="shared" ref="N67:N75" si="3">G67-R67</f>
+        <v>19.855</v>
+      </c>
+      <c r="O67" s="9">
+        <v>-1.7000000000000001E-2</v>
+      </c>
+      <c r="P67" s="9">
+        <v>8.9830000000000005</v>
+      </c>
+      <c r="Q67" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R67" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S67" s="2">
+        <v>6</v>
+      </c>
+      <c r="T67" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U67" s="2">
+        <v>34</v>
+      </c>
+      <c r="V67" s="2">
+        <v>1.0089999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="L68" s="6">
+        <f t="shared" si="2"/>
+        <v>23.78</v>
+      </c>
+      <c r="M68" s="6">
+        <f t="shared" si="2"/>
+        <v>23.78</v>
+      </c>
+      <c r="N68" s="2">
+        <f t="shared" si="3"/>
+        <v>19.844999999999999</v>
+      </c>
+      <c r="O68" s="9">
+        <v>-1.327</v>
+      </c>
+      <c r="P68" s="9">
+        <v>10.292999999999999</v>
+      </c>
+      <c r="Q68" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R68" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S68" s="2">
+        <v>6</v>
+      </c>
+      <c r="T68" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U68" s="2">
+        <v>34</v>
+      </c>
+      <c r="V68" s="2">
+        <v>1.0049999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="L69" s="6">
+        <f t="shared" si="2"/>
+        <v>23.770000000000003</v>
+      </c>
+      <c r="M69" s="6">
+        <f t="shared" si="2"/>
+        <v>23.770000000000003</v>
+      </c>
+      <c r="N69" s="2">
+        <f t="shared" si="3"/>
+        <v>19.835000000000001</v>
+      </c>
+      <c r="O69" s="9">
+        <v>-0.997</v>
+      </c>
+      <c r="P69" s="9">
+        <v>9.9629999999999992</v>
+      </c>
+      <c r="Q69" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R69" s="2">
+        <v>3.7349999999999999</v>
+      </c>
+      <c r="S69" s="2">
+        <v>6</v>
+      </c>
+      <c r="T69" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U69" s="2">
+        <v>34</v>
+      </c>
+      <c r="V69" s="2">
+        <v>0.88500000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="J70" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="K70" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="L70" s="6">
+        <f t="shared" si="2"/>
+        <v>23.75</v>
+      </c>
+      <c r="M70" s="6">
+        <f t="shared" si="2"/>
+        <v>23.75</v>
+      </c>
+      <c r="N70" s="2">
+        <f t="shared" si="3"/>
+        <v>19.251000000000001</v>
+      </c>
+      <c r="O70" s="9">
+        <v>-1.589</v>
+      </c>
+      <c r="P70" s="9">
+        <v>8.891</v>
+      </c>
+      <c r="Q70" s="2" t="s">
+        <v>577</v>
+      </c>
+      <c r="R70" s="2">
+        <v>4.2990000000000004</v>
+      </c>
+      <c r="S70" s="2">
+        <v>7</v>
+      </c>
+      <c r="T70" s="2">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="U70" s="2">
+        <v>34</v>
+      </c>
+      <c r="V70" s="2">
+        <v>1.256</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="L71" s="6">
+        <f t="shared" si="2"/>
+        <v>23.740000000000002</v>
+      </c>
+      <c r="M71" s="6">
+        <f t="shared" si="2"/>
+        <v>23.740000000000002</v>
+      </c>
+      <c r="N71" s="2">
         <f t="shared" si="3"/>
         <v>19.241</v>
       </c>
-      <c r="O49" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P49" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q49" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R49" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S49" s="2">
-        <v>6</v>
-      </c>
-      <c r="T49" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U49" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="50" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="G50" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="L50" s="6">
-        <f t="shared" si="0"/>
-        <v>24.310000000000002</v>
-      </c>
-      <c r="M50" s="6">
-        <f t="shared" si="0"/>
-        <v>24.310000000000002</v>
-      </c>
-      <c r="N50" s="2">
-        <f t="shared" si="3"/>
-        <v>19.210999999999999</v>
-      </c>
-      <c r="O50" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P50" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q50" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R50" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S50" s="2">
-        <v>6</v>
-      </c>
-      <c r="T50" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U50" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="J51" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="K51" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="L51" s="6">
-        <f t="shared" si="0"/>
-        <v>24.270000000000003</v>
-      </c>
-      <c r="M51" s="6">
-        <f t="shared" si="0"/>
-        <v>24.270000000000003</v>
-      </c>
-      <c r="N51" s="2">
-        <f t="shared" si="3"/>
-        <v>19.170999999999999</v>
-      </c>
-      <c r="O51" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P51" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q51" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R51" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S51" s="2">
-        <v>6</v>
-      </c>
-      <c r="T51" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U51" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="G52" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="J52" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="K52" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="L52" s="6">
-        <f t="shared" si="0"/>
-        <v>24.25</v>
-      </c>
-      <c r="M52" s="6">
-        <f t="shared" si="0"/>
-        <v>24.25</v>
-      </c>
-      <c r="N52" s="2">
-        <f t="shared" si="3"/>
-        <v>19.151</v>
-      </c>
-      <c r="O52" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P52" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q52" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R52" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S52" s="2">
-        <v>6</v>
-      </c>
-      <c r="T52" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U52" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="53" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="J53" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="K53" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="L53" s="6">
-        <f t="shared" si="0"/>
-        <v>24.220000000000002</v>
-      </c>
-      <c r="M53" s="6">
-        <f t="shared" si="0"/>
-        <v>24.220000000000002</v>
-      </c>
-      <c r="N53" s="2">
-        <f t="shared" si="3"/>
-        <v>19.120999999999999</v>
-      </c>
-      <c r="O53" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P53" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q53" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R53" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S53" s="2">
-        <v>6</v>
-      </c>
-      <c r="T53" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U53" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="54" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="J54" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K54" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L54" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="M54" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="N54" s="2">
-        <f t="shared" si="3"/>
-        <v>19.070999999999998</v>
-      </c>
-      <c r="O54" s="9">
-        <v>-1.117</v>
-      </c>
-      <c r="P54" s="9">
-        <v>6.883</v>
-      </c>
-      <c r="Q54" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R54" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S54" s="2">
-        <v>6</v>
-      </c>
-      <c r="T54" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U54" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="55" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="J55" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K55" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L55" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="M55" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="N55" s="2">
-        <f t="shared" si="3"/>
-        <v>19.050999999999998</v>
-      </c>
-      <c r="O55" s="9">
-        <v>-1.1519999999999999</v>
-      </c>
-      <c r="P55" s="9">
-        <v>6.8479999999999999</v>
-      </c>
-      <c r="Q55" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R55" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S55" s="2">
-        <v>6</v>
-      </c>
-      <c r="T55" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U55" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="56" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H56" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L56" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="M56" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="N56" s="2">
-        <f t="shared" si="3"/>
-        <v>19.050999999999998</v>
-      </c>
-      <c r="O56" s="9">
-        <v>-1.1519999999999999</v>
-      </c>
-      <c r="P56" s="9">
-        <v>6.8479999999999999</v>
-      </c>
-      <c r="Q56" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R56" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S56" s="2">
-        <v>6</v>
-      </c>
-      <c r="T56" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U56" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="J57" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K57" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L57" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="M57" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="N57" s="2">
-        <f t="shared" si="3"/>
-        <v>19.050999999999998</v>
-      </c>
-      <c r="O57" s="9">
-        <v>-1.1519999999999999</v>
-      </c>
-      <c r="P57" s="9">
-        <v>6.8479999999999999</v>
-      </c>
-      <c r="Q57" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R57" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S57" s="2">
-        <v>6</v>
-      </c>
-      <c r="T57" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U57" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="L58" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="M58" s="6">
-        <f t="shared" si="0"/>
-        <v>25.240000000000002</v>
-      </c>
-      <c r="N58" s="2">
-        <f t="shared" si="3"/>
-        <v>19.041</v>
-      </c>
-      <c r="O58" s="9">
-        <v>-0.67100000000000004</v>
-      </c>
-      <c r="P58" s="9">
-        <v>6.8289999999999997</v>
-      </c>
-      <c r="Q58" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R58" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S58" s="2">
-        <v>6</v>
-      </c>
-      <c r="T58" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U58" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="59" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E59" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="J59" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="K59" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="L59" s="6">
-        <f t="shared" si="0"/>
-        <v>24.05</v>
-      </c>
-      <c r="M59" s="6">
-        <f t="shared" si="0"/>
-        <v>24.05</v>
-      </c>
-      <c r="N59" s="2">
-        <f t="shared" si="3"/>
-        <v>18.951000000000001</v>
-      </c>
-      <c r="O59" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P59" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q59" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R59" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S59" s="2">
-        <v>6</v>
-      </c>
-      <c r="T59" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U59" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E60" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="F60" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="H60" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="K60" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="L60" s="6">
-        <f t="shared" si="0"/>
-        <v>23.970000000000002</v>
-      </c>
-      <c r="M60" s="6">
-        <f t="shared" si="0"/>
-        <v>23.970000000000002</v>
-      </c>
-      <c r="N60" s="2">
-        <f t="shared" si="3"/>
-        <v>18.870999999999999</v>
-      </c>
-      <c r="O60" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P60" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q60" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R60" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S60" s="2">
-        <v>6</v>
-      </c>
-      <c r="T60" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U60" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="61" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>412</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="L61" s="6">
-        <f t="shared" si="0"/>
-        <v>23.94</v>
-      </c>
-      <c r="M61" s="6">
-        <f t="shared" si="0"/>
-        <v>23.94</v>
-      </c>
-      <c r="N61" s="2">
-        <f t="shared" si="3"/>
-        <v>18.840999999999998</v>
-      </c>
-      <c r="O61" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P61" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q61" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R61" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S61" s="2">
-        <v>6</v>
-      </c>
-      <c r="T61" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U61" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="62" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="E62" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F62" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="L62" s="6">
-        <f t="shared" si="0"/>
-        <v>23.92</v>
-      </c>
-      <c r="M62" s="6">
-        <f t="shared" si="0"/>
-        <v>23.92</v>
-      </c>
-      <c r="N62" s="2">
-        <f t="shared" si="3"/>
-        <v>18.820999999999998</v>
-      </c>
-      <c r="O62" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P62" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q62" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R62" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S62" s="2">
-        <v>6</v>
-      </c>
-      <c r="T62" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U62" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="63" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C63" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="L63" s="6">
-        <f t="shared" si="0"/>
-        <v>23.89</v>
-      </c>
-      <c r="M63" s="6">
-        <f t="shared" si="0"/>
-        <v>23.89</v>
-      </c>
-      <c r="N63" s="2">
-        <f t="shared" si="3"/>
-        <v>18.791</v>
-      </c>
-      <c r="O63" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P63" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q63" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R63" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S63" s="2">
-        <v>6</v>
-      </c>
-      <c r="T63" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U63" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="64" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E64" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="F64" s="2" t="s">
-        <v>433</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="H64" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L64" s="6">
-        <f t="shared" si="0"/>
-        <v>23.860000000000003</v>
-      </c>
-      <c r="M64" s="6">
-        <f t="shared" si="0"/>
-        <v>23.860000000000003</v>
-      </c>
-      <c r="N64" s="2">
-        <f t="shared" si="3"/>
-        <v>18.760999999999999</v>
-      </c>
-      <c r="O64" s="9">
-        <v>0.5</v>
-      </c>
-      <c r="P64" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q64" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R64" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S64" s="2">
-        <v>6</v>
-      </c>
-      <c r="T64" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U64" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="65" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="K65" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="L65" s="6">
-        <f t="shared" si="0"/>
-        <v>23.860000000000003</v>
-      </c>
-      <c r="M65" s="6">
-        <f t="shared" si="0"/>
-        <v>23.860000000000003</v>
-      </c>
-      <c r="N65" s="2">
-        <f t="shared" si="3"/>
-        <v>18.760999999999999</v>
-      </c>
-      <c r="O65" s="9">
-        <v>0.48299999999999998</v>
-      </c>
-      <c r="P65" s="9">
-        <v>8.4830000000000005</v>
-      </c>
-      <c r="Q65" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R65" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S65" s="2">
-        <v>6</v>
-      </c>
-      <c r="T65" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U65" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="66" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="I66" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="J66" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="K66" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="L66" s="6">
-        <f t="shared" si="0"/>
-        <v>23.82</v>
-      </c>
-      <c r="M66" s="6">
-        <f t="shared" si="0"/>
-        <v>23.82</v>
-      </c>
-      <c r="N66" s="2">
-        <f t="shared" si="3"/>
-        <v>18.721</v>
-      </c>
-      <c r="O66" s="9">
-        <v>0.20300000000000001</v>
-      </c>
-      <c r="P66" s="9">
-        <v>8.7629999999999999</v>
-      </c>
-      <c r="Q66" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R66" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S66" s="2">
-        <v>6</v>
-      </c>
-      <c r="T66" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U66" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="67" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="L67" s="6">
-        <f t="shared" ref="L67:M81" si="4">J67-0.4</f>
-        <v>23.790000000000003</v>
-      </c>
-      <c r="M67" s="6">
-        <f t="shared" si="4"/>
-        <v>23.790000000000003</v>
-      </c>
-      <c r="N67" s="2">
-        <f t="shared" si="3"/>
-        <v>18.690999999999999</v>
-      </c>
-      <c r="O67" s="9">
-        <v>-1.7000000000000001E-2</v>
-      </c>
-      <c r="P67" s="9">
-        <v>8.9830000000000005</v>
-      </c>
-      <c r="Q67" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R67" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S67" s="2">
-        <v>6</v>
-      </c>
-      <c r="T67" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U67" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="68" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="H68" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="L68" s="6">
-        <f t="shared" si="4"/>
-        <v>23.78</v>
-      </c>
-      <c r="M68" s="6">
-        <f t="shared" si="4"/>
-        <v>23.78</v>
-      </c>
-      <c r="N68" s="2">
-        <f t="shared" si="3"/>
-        <v>18.680999999999997</v>
-      </c>
-      <c r="O68" s="9">
-        <v>-1.327</v>
-      </c>
-      <c r="P68" s="9">
-        <v>10.292999999999999</v>
-      </c>
-      <c r="Q68" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R68" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S68" s="2">
-        <v>6</v>
-      </c>
-      <c r="T68" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U68" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="69" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="L69" s="6">
-        <f t="shared" si="4"/>
-        <v>23.770000000000003</v>
-      </c>
-      <c r="M69" s="6">
-        <f t="shared" si="4"/>
-        <v>23.770000000000003</v>
-      </c>
-      <c r="N69" s="2">
-        <f t="shared" si="3"/>
-        <v>18.670999999999999</v>
-      </c>
-      <c r="O69" s="9">
-        <v>-0.997</v>
-      </c>
-      <c r="P69" s="9">
-        <v>9.9629999999999992</v>
-      </c>
-      <c r="Q69" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R69" s="2">
-        <v>3.7349999999999999</v>
-      </c>
-      <c r="S69" s="2">
-        <v>6</v>
-      </c>
-      <c r="T69" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U69" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="L70" s="6">
-        <f t="shared" si="4"/>
-        <v>23.75</v>
-      </c>
-      <c r="M70" s="6">
-        <f t="shared" si="4"/>
-        <v>23.75</v>
-      </c>
-      <c r="N70" s="2">
-        <f t="shared" si="3"/>
-        <v>18.651</v>
-      </c>
-      <c r="O70" s="9">
-        <v>-1.589</v>
-      </c>
-      <c r="P70" s="9">
-        <v>8.891</v>
-      </c>
-      <c r="Q70" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="R70" s="2">
-        <v>4.2990000000000004</v>
-      </c>
-      <c r="S70" s="2">
-        <v>7</v>
-      </c>
-      <c r="T70" s="2">
-        <v>1.1479999999999999</v>
-      </c>
-      <c r="U70" s="2">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="D71" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="L71" s="6">
-        <f t="shared" si="4"/>
-        <v>23.740000000000002</v>
-      </c>
-      <c r="M71" s="6">
-        <f t="shared" si="4"/>
-        <v>23.740000000000002</v>
-      </c>
-      <c r="N71" s="2">
-        <f t="shared" si="3"/>
-        <v>18.640999999999998</v>
-      </c>
       <c r="O71" s="9">
         <v>-0.439</v>
       </c>
@@ -7053,8 +7274,11 @@
       <c r="U71" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="72" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V71" s="2">
+        <v>1.099</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>477</v>
       </c>
@@ -7089,16 +7313,16 @@
         <v>340</v>
       </c>
       <c r="L72" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.740000000000002</v>
       </c>
       <c r="M72" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.740000000000002</v>
       </c>
       <c r="N72" s="2">
         <f t="shared" si="3"/>
-        <v>18.640999999999998</v>
+        <v>19.241</v>
       </c>
       <c r="O72" s="9">
         <v>-0.48599999999999999</v>
@@ -7121,8 +7345,11 @@
       <c r="U72" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="73" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V72" s="2">
+        <v>1.113</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>482</v>
       </c>
@@ -7157,16 +7384,16 @@
         <v>488</v>
       </c>
       <c r="L73" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.720000000000002</v>
       </c>
       <c r="M73" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.720000000000002</v>
       </c>
       <c r="N73" s="2">
         <f t="shared" si="3"/>
-        <v>18.620999999999999</v>
+        <v>19.221</v>
       </c>
       <c r="O73" s="9">
         <v>-0.34899999999999998</v>
@@ -7189,8 +7416,11 @@
       <c r="U73" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="74" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V73" s="2">
+        <v>0.96099999999999997</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>489</v>
       </c>
@@ -7225,16 +7455,16 @@
         <v>137</v>
       </c>
       <c r="L74" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.71</v>
       </c>
       <c r="M74" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.71</v>
       </c>
       <c r="N74" s="2">
         <f t="shared" si="3"/>
-        <v>18.611000000000001</v>
+        <v>19.211000000000002</v>
       </c>
       <c r="O74" s="9">
         <v>-0.34899999999999998</v>
@@ -7257,8 +7487,11 @@
       <c r="U74" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="75" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V74" s="2">
+        <v>0.84099999999999997</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>35</v>
       </c>
@@ -7293,16 +7526,16 @@
         <v>498</v>
       </c>
       <c r="L75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.700000000000003</v>
       </c>
       <c r="M75" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.700000000000003</v>
       </c>
       <c r="N75" s="2">
         <f t="shared" si="3"/>
-        <v>18.600999999999999</v>
+        <v>18.655999999999999</v>
       </c>
       <c r="O75" s="9">
         <v>-1.181</v>
@@ -7325,8 +7558,11 @@
       <c r="U75" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="76" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V75" s="2">
+        <v>1.3540000000000001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>499</v>
       </c>
@@ -7361,16 +7597,16 @@
         <v>91</v>
       </c>
       <c r="L76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.69</v>
       </c>
       <c r="M76" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.69</v>
       </c>
       <c r="N76" s="2">
-        <f t="shared" si="3"/>
-        <v>18.590999999999998</v>
+        <f t="shared" ref="N76:N79" si="4">G76-R76</f>
+        <v>18.645999999999997</v>
       </c>
       <c r="O76" s="9">
         <v>-1.181</v>
@@ -7393,8 +7629,11 @@
       <c r="U76" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="77" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V76" s="2">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>505</v>
       </c>
@@ -7429,16 +7668,16 @@
         <v>117</v>
       </c>
       <c r="L77" s="6">
+        <f t="shared" si="2"/>
+        <v>23.68</v>
+      </c>
+      <c r="M77" s="6">
+        <f t="shared" si="2"/>
+        <v>23.68</v>
+      </c>
+      <c r="N77" s="2">
         <f t="shared" si="4"/>
-        <v>23.68</v>
-      </c>
-      <c r="M77" s="6">
-        <f t="shared" si="4"/>
-        <v>23.68</v>
-      </c>
-      <c r="N77" s="2">
-        <f t="shared" si="3"/>
-        <v>18.581</v>
+        <v>18.635999999999999</v>
       </c>
       <c r="O77" s="11">
         <v>-0.70099999999999996</v>
@@ -7461,8 +7700,11 @@
       <c r="U77" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="78" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V77" s="2">
+        <v>1.242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>61</v>
       </c>
@@ -7497,16 +7739,16 @@
         <v>125</v>
       </c>
       <c r="L78" s="6">
+        <f t="shared" si="2"/>
+        <v>23.67</v>
+      </c>
+      <c r="M78" s="6">
+        <f t="shared" si="2"/>
+        <v>23.67</v>
+      </c>
+      <c r="N78" s="2">
         <f t="shared" si="4"/>
-        <v>23.67</v>
-      </c>
-      <c r="M78" s="6">
-        <f t="shared" si="4"/>
-        <v>23.67</v>
-      </c>
-      <c r="N78" s="2">
-        <f t="shared" si="3"/>
-        <v>18.570999999999998</v>
+        <v>18.625999999999998</v>
       </c>
       <c r="O78" s="11">
         <v>7.9000000000000001E-2</v>
@@ -7529,8 +7771,11 @@
       <c r="U78" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="79" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V78" s="2">
+        <v>1.1839999999999999</v>
+      </c>
+    </row>
+    <row r="79" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>518</v>
       </c>
@@ -7565,16 +7810,16 @@
         <v>164</v>
       </c>
       <c r="L79" s="6">
+        <f t="shared" si="2"/>
+        <v>23.66</v>
+      </c>
+      <c r="M79" s="6">
+        <f t="shared" si="2"/>
+        <v>23.66</v>
+      </c>
+      <c r="N79" s="2">
         <f t="shared" si="4"/>
-        <v>23.66</v>
-      </c>
-      <c r="M79" s="6">
-        <f t="shared" si="4"/>
-        <v>23.66</v>
-      </c>
-      <c r="N79" s="2">
-        <f t="shared" si="3"/>
-        <v>18.561</v>
+        <v>18.616</v>
       </c>
       <c r="O79" s="9">
         <v>0.219</v>
@@ -7597,8 +7842,11 @@
       <c r="U79" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="80" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V79" s="2">
+        <v>1.212</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>524</v>
       </c>
@@ -7633,16 +7881,16 @@
         <v>498</v>
       </c>
       <c r="L80" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.700000000000003</v>
       </c>
       <c r="M80" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.700000000000003</v>
       </c>
       <c r="N80" s="2">
-        <f t="shared" si="3"/>
-        <v>18.471</v>
+        <f>G80-R80</f>
+        <v>18.526</v>
       </c>
       <c r="O80" s="20">
         <v>0.51300000000000001</v>
@@ -7665,8 +7913,11 @@
       <c r="U80" s="2">
         <v>34</v>
       </c>
-    </row>
-    <row r="81" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V80" s="2">
+        <v>1.4019999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>383</v>
       </c>
@@ -7701,11 +7952,11 @@
         <v>178</v>
       </c>
       <c r="L81" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.5</v>
       </c>
       <c r="M81" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>23.5</v>
       </c>
       <c r="N81" s="13"/>
@@ -7718,8 +7969,9 @@
       <c r="S81" s="13"/>
       <c r="T81" s="13"/>
       <c r="U81" s="13"/>
-    </row>
-    <row r="82" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V81" s="2"/>
+    </row>
+    <row r="82" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>532</v>
       </c>
@@ -7765,8 +8017,9 @@
       <c r="S82" s="14"/>
       <c r="T82" s="14"/>
       <c r="U82" s="14"/>
-    </row>
-    <row r="83" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V82" s="2"/>
+    </row>
+    <row r="83" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>534</v>
       </c>
@@ -7812,8 +8065,9 @@
       <c r="S83" s="14"/>
       <c r="T83" s="14"/>
       <c r="U83" s="14"/>
-    </row>
-    <row r="84" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V83" s="2"/>
+    </row>
+    <row r="84" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>536</v>
       </c>
@@ -7874,8 +8128,11 @@
       <c r="U84" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="85" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V84" s="2">
+        <v>0.96599999999999997</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>542</v>
       </c>
@@ -7936,8 +8193,11 @@
       <c r="U85" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="86" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V85" s="2">
+        <v>1.0900000000000001</v>
+      </c>
+    </row>
+    <row r="86" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>546</v>
       </c>
@@ -7998,8 +8258,11 @@
       <c r="U86" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="87" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V86" s="2">
+        <v>0.98799999999999999</v>
+      </c>
+    </row>
+    <row r="87" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>553</v>
       </c>
@@ -8060,8 +8323,9 @@
       <c r="U87" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="88" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V87" s="2"/>
+    </row>
+    <row r="88" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>560</v>
       </c>
@@ -8120,8 +8384,9 @@
       <c r="U88" s="2">
         <v>27</v>
       </c>
-    </row>
-    <row r="89" spans="1:21" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="V88" s="2"/>
+    </row>
+    <row r="89" spans="1:22" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>35</v>
       </c>
@@ -8180,6 +8445,7 @@
       <c r="U89" s="2">
         <v>27</v>
       </c>
+      <c r="V89" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
